--- a/testakten/schriftform-mietkuendigung-bielefeld-online-pferdedrescher/Aufstellung_Kosten_und_Schaeden.xlsx
+++ b/testakten/schriftform-mietkuendigung-bielefeld-online-pferdedrescher/Aufstellung_Kosten_und_Schaeden.xlsx
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -693,10 +693,11 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FIKTIVE TESTAKTE -- Plugin: schriftform-und-textform-bgb</t>
-        </is>
-      </c>
-    </row>
+          <t>Mandatsakte Pferdedrescher-Riesenstein gegen Eberhart-Wolframshausen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -787,6 +788,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -904,6 +906,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
@@ -998,6 +1001,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
@@ -1109,6 +1113,7 @@
       <c r="E32" s="18" t="n"/>
       <c r="F32" s="19" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
